--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484287_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484287_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3232</v>
+        <v>3.3196</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5712</v>
+        <v>1.8945</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7519</v>
+        <v>1.4251</v>
       </c>
       <c r="G2" t="n">
         <v>2.276</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9333</v>
+        <v>-0.9369</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.2185</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3915</v>
+        <v>-0.7183</v>
       </c>
       <c r="V2" t="n">
         <v>0.2224</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.251</v>
+        <v>0.8425</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9351</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1862</v>
+        <v>1.7776</v>
       </c>
       <c r="G3" t="n">
         <v>0.1529</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.234</v>
+        <v>-0.6425</v>
       </c>
       <c r="T3" t="n">
         <v>-0.6657</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4318</v>
+        <v>0.0233</v>
       </c>
       <c r="V3" t="n">
         <v>0.9414</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1084</v>
+        <v>0.2577</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0545</v>
+        <v>-0.9335</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9461000000000001</v>
+        <v>1.1912</v>
       </c>
       <c r="G4" t="n">
         <v>2.2009</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0554</v>
+        <v>-0.6892</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7125</v>
+        <v>-0.5915</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3429</v>
+        <v>-0.0978</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4843</v>
+        <v>-0.1399</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.3224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1008</v>
+        <v>0.1825</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4178</v>
@@ -844,13 +844,13 @@
         <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4573</v>
+        <v>-0.1128</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0275</v>
+        <v>0.2903</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4848</v>
+        <v>-0.4031</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2333</v>
+        <v>-0.7431</v>
       </c>
       <c r="E6" t="n">
         <v>0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2733</v>
+        <v>-0.7831</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6466</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4229</v>
+        <v>-0.9327</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2667</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1562</v>
+        <v>-0.666</v>
       </c>
       <c r="V6" t="n">
         <v>0.0549</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5283</v>
+        <v>-2.6375</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7357</v>
+        <v>-2.5661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2074</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5705</v>
+        <v>-1.2164</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8264</v>
+        <v>-1.5265</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2558</v>
+        <v>0.3101</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1078</v>
+        <v>-1.2668</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.095</v>
+        <v>-0.6332</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0128</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4627</v>
+        <v>0.0504</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7314</v>
+        <v>-0.8933</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2687</v>
+        <v>0.9437</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4367</v>
+        <v>-0.5579</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8064</v>
+        <v>-0.3225</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6303</v>
+        <v>-0.2353</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1089</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8203</v>
+        <v>-2.9788</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6672</v>
+        <v>-2.4236</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1531</v>
+        <v>-0.5552</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2164</v>
+        <v>-2.5705</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5265</v>
+        <v>-2.8264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3101</v>
+        <v>0.2558</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2668</v>
+        <v>-1.1078</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6332</v>
+        <v>-1.095</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.0128</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0504</v>
+        <v>-1.4627</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8933</v>
+        <v>-1.7314</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9437</v>
+        <v>0.2687</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7407</v>
+        <v>-0.0138</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4237</v>
+        <v>0.1185</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.317</v>
+        <v>-0.1323</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-1.1089</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3892</v>
+        <v>-3.3246</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9898</v>
+        <v>-5.3338</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6006</v>
+        <v>2.0092</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2597</v>
@@ -1156,13 +1156,13 @@
         <v>2.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.161</v>
+        <v>-1.0964</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1185</v>
+        <v>-0.2254</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2795</v>
+        <v>-0.871</v>
       </c>
       <c r="V9" t="n">
         <v>0.0549</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7337</v>
+        <v>-3.7142</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.3253</v>
+        <v>-5.4965</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5916</v>
+        <v>1.7822</v>
       </c>
       <c r="G10" t="n">
         <v>-2.286</v>
@@ -1234,13 +1234,13 @@
         <v>2.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3381</v>
+        <v>-1.3186</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5185</v>
+        <v>-0.6896</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8196</v>
+        <v>-0.6289</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1097</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.7233</v>
+        <v>-9.118300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-16.6816</v>
+        <v>-16.0765</v>
       </c>
       <c r="F11" t="n">
-        <v>6.958199999999999</v>
+        <v>6.9581</v>
       </c>
       <c r="G11" t="n">
         <v>-5.767199999999999</v>
@@ -1288,7 +1288,7 @@
         <v>-3.8221</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4555</v>
+        <v>-0.4555000000000005</v>
       </c>
       <c r="L11" t="n">
         <v>-3.3665</v>
@@ -1312,10 +1312,10 @@
         <v>15.6274</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.906</v>
+        <v>-6.300800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1765</v>
+        <v>-2.5711</v>
       </c>
       <c r="U11" t="n">
         <v>-3.7294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4146</v>
+        <v>11.3988</v>
       </c>
       <c r="E12" t="n">
-        <v>9.405200000000001</v>
+        <v>6.8773</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0095</v>
+        <v>4.5215</v>
       </c>
       <c r="G12" t="n">
         <v>6.7944</v>
@@ -1390,13 +1390,13 @@
         <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5849</v>
+        <v>2.5691</v>
       </c>
       <c r="T12" t="n">
-        <v>4.0145</v>
+        <v>1.4867</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5704</v>
+        <v>1.0824</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4051</v>
+        <v>4.1285</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5053</v>
+        <v>1.6064</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8997</v>
+        <v>2.5221</v>
       </c>
       <c r="G13" t="n">
         <v>3.435</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2938</v>
+        <v>1.0173</v>
       </c>
       <c r="T13" t="n">
-        <v>0.091</v>
+        <v>0.1921</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2029</v>
+        <v>0.8252</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4959</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8482</v>
+        <v>3.6401</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3506</v>
+        <v>-0.7439</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1987</v>
+        <v>4.384</v>
       </c>
       <c r="G14" t="n">
         <v>2.5771</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0487</v>
+        <v>1.8406</v>
       </c>
       <c r="T14" t="n">
-        <v>0.091</v>
+        <v>0.6977</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9577</v>
+        <v>1.1429</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3869</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7855</v>
+        <v>2.1143</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2351</v>
+        <v>-1.1229</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0206</v>
+        <v>3.2371</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6944</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2895</v>
+        <v>1.0393</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.773</v>
+        <v>0.3392</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4836</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>2.16</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1916</v>
+        <v>1.4595</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8927</v>
+        <v>-0.0838</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0843</v>
+        <v>1.5433</v>
       </c>
       <c r="G16" t="n">
         <v>0.5502</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9679</v>
+        <v>0.2999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9684</v>
+        <v>-0.1594</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004</v>
+        <v>0.4593</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3889</v>
+        <v>-1.8111</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4341</v>
+        <v>-3.0517</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0452</v>
+        <v>1.2406</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2545</v>
+        <v>-2.5611</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3891</v>
+        <v>-0.7549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1346</v>
+        <v>-1.8062</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0399</v>
+        <v>-2.6064</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0399</v>
+        <v>0.1433</v>
       </c>
       <c r="L17" t="n">
+        <v>-2.7497</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.8982</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>-0.2146</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.3492</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-4.2975</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-4.8836</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5539</v>
+        <v>0.5193</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2122</v>
+        <v>-0.0583</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3416</v>
+        <v>0.5777</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6093</v>
+        <v>-0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOY BASSOLS</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5408</v>
+        <v>-2.1714</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9416</v>
+        <v>-4.5473</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5992</v>
+        <v>2.3758</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.679</v>
+        <v>-2.4006</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9486</v>
+        <v>-1.1471</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2696</v>
+        <v>-1.2535</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6741</v>
+        <v>-2.9751</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6741</v>
+        <v>-1.5874</v>
       </c>
       <c r="L18" t="n">
+        <v>-1.3877</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>-0.0049</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.2745</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.2696</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3335</v>
+        <v>0.8384</v>
       </c>
       <c r="T18" t="n">
-        <v>0.432</v>
+        <v>0.104</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0985</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
         <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>M. SOY BASSOLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.83</v>
+        <v>-2.7897</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9617</v>
+        <v>-1.2449</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1317</v>
+        <v>-1.5448</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5611</v>
+        <v>-0.679</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7549</v>
+        <v>-0.9486</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8062</v>
+        <v>0.2696</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6064</v>
+        <v>-0.6741</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1433</v>
+        <v>-0.6741</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.7497</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0454</v>
+        <v>-0.0049</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8982</v>
+        <v>-0.2745</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9435</v>
+        <v>0.2696</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.1721</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.4996</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9684</v>
+        <v>0.1287</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4687</v>
+        <v>-0.044</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1618</v>
+        <v>-3.5491</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0528</v>
+        <v>-4.6474</v>
       </c>
       <c r="F20" t="n">
-        <v>1.891</v>
+        <v>1.0983</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4006</v>
+        <v>-1.2545</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1471</v>
+        <v>-1.3891</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2535</v>
+        <v>0.1346</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9751</v>
+        <v>-1.0399</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5874</v>
+        <v>-1.0399</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3877</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5745</v>
+        <v>-0.2146</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4403</v>
+        <v>-0.3492</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1342</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-4.2975</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1519</v>
+        <v>1.3936</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4015</v>
+        <v>0.9988</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2496</v>
+        <v>0.3948</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
         <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="21">
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>9.723500000000001</v>
+        <v>12.4199</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.9581</v>
+        <v>-6.958199999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>16.6815</v>
+        <v>19.3779</v>
       </c>
       <c r="G21" t="n">
-        <v>5.7671</v>
+        <v>5.767099999999999</v>
       </c>
       <c r="H21" t="n">
         <v>7.1145</v>
@@ -2077,7 +2077,7 @@
         <v>3.8221</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4557000000000001</v>
+        <v>0.4557000000000002</v>
       </c>
       <c r="O21" t="n">
         <v>3.3664</v>
@@ -2092,13 +2092,13 @@
         <v>13.674</v>
       </c>
       <c r="S21" t="n">
-        <v>6.9059</v>
+        <v>9.6021</v>
       </c>
       <c r="T21" t="n">
-        <v>3.7294</v>
+        <v>3.7295</v>
       </c>
       <c r="U21" t="n">
-        <v>3.1764</v>
+        <v>5.8728</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9963000000000002</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484287_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484287_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8425</v>
+        <v>2.4419</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9351</v>
+        <v>2.4419</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7776</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1529</v>
+        <v>2.4419</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3323</v>
+        <v>1.2279</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4852</v>
+        <v>1.214</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5113</v>
+        <v>2.4419</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5921999999999999</v>
+        <v>1.2279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0809</v>
+        <v>1.214</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2599</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6425</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6657</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0233</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2577</v>
+        <v>0.8425</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9335</v>
+        <v>-0.9351</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1912</v>
+        <v>1.7776</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2009</v>
+        <v>0.1529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8391</v>
+        <v>-0.3323</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3618</v>
+        <v>0.4852</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6114</v>
+        <v>-0.5113</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9235</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6879</v>
+        <v>0.0809</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5895</v>
+        <v>0.6642</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0844</v>
+        <v>0.2599</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4043</v>
       </c>
       <c r="P4" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6892</v>
+        <v>-0.6425</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5915</v>
+        <v>-0.6657</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0978</v>
+        <v>0.0233</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1399</v>
+        <v>0.2577</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3224</v>
+        <v>-0.9335</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1825</v>
+        <v>1.1912</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4178</v>
+        <v>2.2009</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1215</v>
+        <v>0.8391</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5393</v>
+        <v>1.3618</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6127</v>
+        <v>1.6114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0614</v>
+        <v>0.9235</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6741</v>
+        <v>0.6879</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1949</v>
+        <v>0.5895</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0601</v>
+        <v>-0.0844</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1128</v>
+        <v>-0.6892</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2903</v>
+        <v>-0.5915</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4031</v>
+        <v>-0.0978</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7431</v>
+        <v>-0.1399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>-0.3224</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7831</v>
+        <v>0.1825</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6466</v>
+        <v>-0.4178</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1228</v>
+        <v>0.1215</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7694</v>
+        <v>-0.5393</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0062</v>
+        <v>-0.6127</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6398</v>
+        <v>0.0614</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6528</v>
+        <v>0.1949</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.517</v>
+        <v>0.0601</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1358</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9327</v>
+        <v>-0.1128</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2667</v>
+        <v>0.2903</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.666</v>
+        <v>-0.4031</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6375</v>
+        <v>-0.7431</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5661</v>
+        <v>0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.7831</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2164</v>
+        <v>-0.6466</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5265</v>
+        <v>0.1228</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3101</v>
+        <v>-0.7694</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2668</v>
+        <v>1.0062</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6332</v>
+        <v>1.6398</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0504</v>
+        <v>-1.6528</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8933</v>
+        <v>-1.517</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9437</v>
+        <v>-0.1358</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5579</v>
+        <v>-0.9327</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3225</v>
+        <v>-0.2667</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2353</v>
+        <v>-0.666</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9788</v>
+        <v>-2.6375</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4236</v>
+        <v>-2.5661</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5552</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5705</v>
+        <v>-1.2164</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8264</v>
+        <v>-1.5265</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2558</v>
+        <v>0.3101</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1078</v>
+        <v>-1.2668</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.095</v>
+        <v>-0.6332</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0128</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4627</v>
+        <v>0.0504</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7314</v>
+        <v>-0.8933</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2687</v>
+        <v>0.9437</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0138</v>
+        <v>-0.5579</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1185</v>
+        <v>-0.3225</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1323</v>
+        <v>-0.2353</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1089</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3246</v>
+        <v>-2.9788</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3338</v>
+        <v>-2.4236</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0092</v>
+        <v>-0.5552</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2597</v>
+        <v>-2.5705</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.4897</v>
+        <v>-2.8264</v>
       </c>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0.2558</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.7642</v>
+        <v>-1.1078</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9164</v>
+        <v>-1.095</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8478</v>
+        <v>-0.0128</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5044999999999999</v>
+        <v>-1.4627</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5733</v>
+        <v>-1.7314</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0778</v>
+        <v>0.2687</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9301</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0964</v>
+        <v>-0.0138</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2254</v>
+        <v>0.1185</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.871</v>
+        <v>-0.1323</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0549</v>
+        <v>0.3869</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5545</v>
+        <v>-1.1089</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7142</v>
+        <v>-3.3246</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4965</v>
+        <v>-5.3338</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7822</v>
+        <v>2.0092</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.286</v>
+        <v>-3.2597</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3126</v>
+        <v>-3.4897</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0266</v>
+        <v>0.23</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.767</v>
+        <v>-3.7642</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1205</v>
+        <v>-2.9164</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6465</v>
+        <v>-0.8478</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.519</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1921</v>
+        <v>-0.5733</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6731</v>
+        <v>1.0778</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
         <v>2.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3186</v>
+        <v>-1.0964</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6896</v>
+        <v>-0.2254</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6289</v>
+        <v>-0.871</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1097</v>
+        <v>0.0549</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1097</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.118300000000001</v>
+        <v>-6.1562</v>
       </c>
       <c r="E11" t="n">
-        <v>-16.0765</v>
+        <v>-7.9384</v>
       </c>
       <c r="F11" t="n">
-        <v>6.9581</v>
+        <v>1.7822</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.767199999999999</v>
+        <v>-4.7279</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.1145</v>
+        <v>-3.5406</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3472</v>
+        <v>-1.1873</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8221</v>
+        <v>-4.2089</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4555000000000005</v>
+        <v>-2.3485</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3665</v>
+        <v>-1.8604</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9451</v>
+        <v>-0.519</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.6589</v>
+        <v>-1.1921</v>
       </c>
       <c r="O11" t="n">
-        <v>4.713799999999999</v>
+        <v>0.6731</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9535</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.6738</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>15.6274</v>
+        <v>2.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.300800000000001</v>
+        <v>-1.3186</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.5711</v>
+        <v>-0.6896</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.7294</v>
+        <v>-0.6289</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9964000000000001</v>
+        <v>-0.1097</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9909</v>
+        <v>-0.1097</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9946</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.3988</v>
+        <v>-9.118400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8773</v>
+        <v>-16.0765</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5215</v>
+        <v>6.9581</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7944</v>
+        <v>-5.767200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7834</v>
+        <v>-7.114599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0111</v>
+        <v>1.3473</v>
       </c>
       <c r="J12" t="n">
-        <v>6.0901</v>
+        <v>-3.8221</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3479</v>
+        <v>-0.4556000000000004</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7422</v>
+        <v>-3.366400000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7043</v>
+        <v>-1.9451</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4355</v>
+        <v>-6.658899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2688</v>
+        <v>4.7138</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7581</v>
+        <v>1.9535</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-13.6738</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>15.6274</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5691</v>
+        <v>-6.300800000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4867</v>
+        <v>-2.5711</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0824</v>
+        <v>-3.7294</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>0.9964000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>3.9909</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.9946</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1285</v>
+        <v>11.3988</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6064</v>
+        <v>6.8773</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5221</v>
+        <v>4.5215</v>
       </c>
       <c r="G13" t="n">
-        <v>3.435</v>
+        <v>6.7944</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1535</v>
+        <v>5.7834</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2815</v>
+        <v>1.0111</v>
       </c>
       <c r="J13" t="n">
-        <v>2.391</v>
+        <v>6.0901</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7831</v>
+        <v>5.3479</v>
       </c>
       <c r="L13" t="n">
-        <v>0.608</v>
+        <v>0.7422</v>
       </c>
       <c r="M13" t="n">
-        <v>1.044</v>
+        <v>0.7043</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3705</v>
+        <v>0.4355</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6735</v>
+        <v>0.2688</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0173</v>
+        <v>2.5691</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1921</v>
+        <v>1.4867</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8252</v>
+        <v>1.0824</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6401</v>
+        <v>4.1285</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7439</v>
+        <v>1.6064</v>
       </c>
       <c r="F14" t="n">
-        <v>4.384</v>
+        <v>2.5221</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5771</v>
+        <v>3.435</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7642</v>
+        <v>2.1535</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1871</v>
+        <v>1.2815</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5983</v>
+        <v>2.391</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7846</v>
+        <v>1.7831</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1863</v>
+        <v>0.608</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9788</v>
+        <v>1.044</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9796</v>
+        <v>0.3705</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0008</v>
+        <v>0.6735</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8406</v>
+        <v>1.0173</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6977</v>
+        <v>0.1921</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1429</v>
+        <v>0.8252</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3869</v>
+        <v>-1.4959</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1143</v>
+        <v>3.6401</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1229</v>
+        <v>-0.7439</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2371</v>
+        <v>4.384</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6944</v>
+        <v>2.5771</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6662</v>
+        <v>3.7642</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9718</v>
+        <v>-1.1871</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0045</v>
+        <v>1.5983</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.898</v>
+        <v>2.7846</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1066</v>
+        <v>-1.1863</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3102</v>
+        <v>0.9788</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7682</v>
+        <v>0.9796</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0784</v>
+        <v>-0.0008</v>
       </c>
       <c r="P15" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0393</v>
+        <v>1.8406</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3392</v>
+        <v>0.6977</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7000999999999999</v>
+        <v>1.1429</v>
       </c>
       <c r="V15" t="n">
-        <v>2.16</v>
+        <v>-0.3869</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>-0.1097</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4595</v>
+        <v>2.1143</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0838</v>
+        <v>-1.1229</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5433</v>
+        <v>3.2371</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5502</v>
+        <v>-0.6944</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3193</v>
+        <v>-1.6662</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.769</v>
+        <v>0.9718</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1658</v>
+        <v>-1.0045</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7994</v>
+        <v>-0.898</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.1066</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3844</v>
+        <v>0.3102</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5199</v>
+        <v>-0.7682</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>1.0784</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2999</v>
+        <v>1.0393</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1594</v>
+        <v>0.3392</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4593</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8111</v>
+        <v>1.4595</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0517</v>
+        <v>-0.0838</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2406</v>
+        <v>1.5433</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5611</v>
+        <v>0.5502</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7549</v>
+        <v>1.3193</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8062</v>
+        <v>-0.769</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.6064</v>
+        <v>0.1658</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1433</v>
+        <v>0.7994</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.7497</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0454</v>
+        <v>0.3844</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8982</v>
+        <v>0.5199</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9435</v>
+        <v>-0.1354</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5193</v>
+        <v>0.2999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0583</v>
+        <v>-0.1594</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5777</v>
+        <v>0.4593</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3869</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1714</v>
+        <v>-1.8111</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.5473</v>
+        <v>-3.0517</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3758</v>
+        <v>1.2406</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4006</v>
+        <v>-2.5611</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1471</v>
+        <v>-0.7549</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2535</v>
+        <v>-1.8062</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.9751</v>
+        <v>-2.6064</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5874</v>
+        <v>0.1433</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3877</v>
+        <v>-2.7497</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5745</v>
+        <v>0.0454</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4403</v>
+        <v>-0.8982</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1342</v>
+        <v>0.9435</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8384</v>
+        <v>0.5193</v>
       </c>
       <c r="T18" t="n">
-        <v>0.104</v>
+        <v>-0.0583</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.5777</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8865</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SOY BASSOLS</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7897</v>
+        <v>-2.1714</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2449</v>
+        <v>-4.5473</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5448</v>
+        <v>2.3758</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.679</v>
+        <v>-2.4006</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9486</v>
+        <v>-1.1471</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2696</v>
+        <v>-1.2535</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6741</v>
+        <v>-2.9751</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6741</v>
+        <v>-1.5874</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.3877</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0049</v>
+        <v>0.5745</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2745</v>
+        <v>0.4403</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>0.1342</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.8384</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1287</v>
+        <v>0.104</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.044</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
         <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>M. SOY BASSOLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5491</v>
+        <v>-2.7897</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6474</v>
+        <v>-1.2449</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0983</v>
+        <v>-1.5448</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2545</v>
+        <v>-0.679</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3891</v>
+        <v>-0.9486</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1346</v>
+        <v>0.2696</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0399</v>
+        <v>-0.6741</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0399</v>
+        <v>-0.6741</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2146</v>
+        <v>-0.0049</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3492</v>
+        <v>-0.2745</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>0.2696</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.2975</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3936</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9988</v>
+        <v>0.1287</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3948</v>
+        <v>-0.044</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,152 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-3.5491</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.6474</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.0983</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.2545</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.3891</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.0399</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.0399</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.2146</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-4.2975</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484287_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>12.4199</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>-6.958199999999999</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>19.3779</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>5.767099999999999</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>7.1145</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>-1.3472</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1.945199999999999</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>6.6589</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>-4.713699999999999</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>3.8221</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>0.4557000000000002</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>3.3664</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>-1.9533</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>13.674</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>9.6021</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3.7295</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>5.8728</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>-0.9963000000000002</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W22" t="n">
         <v>2.9946</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>-3.9909</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
